--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/Tutorial.xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/Tutorial.xlsx
@@ -562,11 +562,7 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Player_Normal</t>
-        </is>
-      </c>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Player_Normal</t>
@@ -606,11 +602,7 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Player_Normal</t>
-        </is>
-      </c>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Player_Normal</t>
@@ -646,11 +638,7 @@
           <t>Mimi</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Mimi_Angry</t>
-        </is>
-      </c>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Player_Normal</t>
@@ -758,11 +746,7 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Player_Normal</t>
-        </is>
-      </c>
+      <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Player_Normal</t>
@@ -802,11 +786,7 @@
           <t>Mimi</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Mimi_Angry</t>
-        </is>
-      </c>
+      <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Player_Normal</t>
